--- a/artfynd/A 6252-2024 artfynd.xlsx
+++ b/artfynd/A 6252-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>115020131</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115020252</v>
+        <v>115020110</v>
       </c>
       <c r="B3" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>396087</v>
+        <v>395913</v>
       </c>
       <c r="R3" t="n">
-        <v>6440572</v>
+        <v>6440528</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +861,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Grusås med glest trädskikt av bl.a björk</t>
+          <t>Talldominerad skog på grusås</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -889,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115020110</v>
+        <v>115020252</v>
       </c>
       <c r="B4" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>395913</v>
+        <v>396087</v>
       </c>
       <c r="R4" t="n">
-        <v>6440528</v>
+        <v>6440572</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +963,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Talldominerad skog på grusås</t>
+          <t>Grusås med glest trädskikt av bl.a björk</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
